--- a/data/excel/salarios.xlsx
+++ b/data/excel/salarios.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P131"/>
+  <dimension ref="A1:P132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6743,6 +6743,56 @@
       </c>
       <c r="P131" t="n">
         <v>36.18095668249821</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B132" t="n">
+        <v>10159.65</v>
+      </c>
+      <c r="C132" t="n">
+        <v>2.83181863728974</v>
+      </c>
+      <c r="D132" t="n">
+        <v>30.42013160563497</v>
+      </c>
+      <c r="E132" t="n">
+        <v>8307.48</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2.260003840529401</v>
+      </c>
+      <c r="G132" t="n">
+        <v>30.30707526379108</v>
+      </c>
+      <c r="H132" t="n">
+        <v>9467.780000000001</v>
+      </c>
+      <c r="I132" t="n">
+        <v>2.64377835020253</v>
+      </c>
+      <c r="J132" t="n">
+        <v>30.38307459467797</v>
+      </c>
+      <c r="K132" t="n">
+        <v>12005.54</v>
+      </c>
+      <c r="L132" t="n">
+        <v>2.998445441161834</v>
+      </c>
+      <c r="M132" t="n">
+        <v>55.35521105618677</v>
+      </c>
+      <c r="N132" t="n">
+        <v>9973.549999999999</v>
+      </c>
+      <c r="O132" t="n">
+        <v>2.728600504293088</v>
+      </c>
+      <c r="P132" t="n">
+        <v>35.61263672013097</v>
       </c>
     </row>
   </sheetData>
@@ -6815,7 +6865,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19T18:11:14Z</t>
+          <t>2026-10-21T19:38:26Z</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6877,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
